--- a/data/trans_orig/Q02D_LAB-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q02D_LAB-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de horas diarias, de lunes a viernes, que dedica la persona entrevistada a cuidar a las personas del hogar que lo necesitan</t>
+          <t>Número medio de horas diarias, de lunes a viernes, que dedica la persona entrevistada a cuidar a las personas del hogar que lo necesitan (tasa de respuesta: 89,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,17 +716,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,71</t>
+          <t>1,79; 3,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,79; 7,5</t>
+          <t>5,86; 7,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,28</t>
+          <t>5,56; 8,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -736,42 +736,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,3</t>
+          <t>2,82; 4,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,1; 9,43</t>
+          <t>8,15; 9,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,11; 12,6</t>
+          <t>10,07; 12,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,05; 9,26</t>
+          <t>4,18; 9,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 3,76</t>
+          <t>2,61; 3,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,43; 8,49</t>
+          <t>7,36; 8,51</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,43; 10,35</t>
+          <t>8,42; 10,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 14,15</t>
+          <t>4,57; 14,03</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,01; 7,26</t>
+          <t>5,07; 7,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,27; 7,37</t>
+          <t>6,22; 7,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,18; 12,58</t>
+          <t>9,4; 12,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -876,42 +876,42 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,67; 9,39</t>
+          <t>7,67; 9,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,47; 8,6</t>
+          <t>7,43; 8,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,86; 13,64</t>
+          <t>10,87; 13,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,49; 13,53</t>
+          <t>8,62; 13,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,98; 8,31</t>
+          <t>6,92; 8,38</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,14; 7,98</t>
+          <t>7,17; 7,97</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,7; 12,76</t>
+          <t>10,73; 12,94</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,05; 14,19</t>
+          <t>9,22; 14,48</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,99</t>
+          <t>1,43; 2,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 3,67</t>
+          <t>2,45; 3,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,24; 9,86</t>
+          <t>7,24; 9,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,33; 20,71</t>
+          <t>10,34; 21,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,1; 4,64</t>
+          <t>3,04; 4,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,16; 5,26</t>
+          <t>4,21; 5,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,39; 12,55</t>
+          <t>9,39; 12,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,56; 15,07</t>
+          <t>8,44; 14,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 3,67</t>
+          <t>2,49; 3,59</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,6; 4,43</t>
+          <t>3,59; 4,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,7; 10,91</t>
+          <t>8,71; 10,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,98; 16,14</t>
+          <t>10,1; 15,95</t>
         </is>
       </c>
     </row>
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,17</t>
+          <t>1,51; 2,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,96; 6,51</t>
+          <t>4,96; 6,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,94; 7,88</t>
+          <t>4,97; 7,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1156,42 +1156,42 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,41; 5,12</t>
+          <t>3,38; 5,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,46; 8,9</t>
+          <t>7,44; 8,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,07; 9,03</t>
+          <t>7,05; 8,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,26; 13,62</t>
+          <t>9,28; 13,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 3,7</t>
+          <t>2,64; 3,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,72; 7,79</t>
+          <t>6,7; 7,76</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,63; 8,25</t>
+          <t>6,56; 8,29</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,95; 11,9</t>
+          <t>7,87; 11,44</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,21; 7,3</t>
+          <t>4,17; 7,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,06; 5,78</t>
+          <t>4,05; 5,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,8; 3,67</t>
+          <t>2,8; 3,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,69; 4,37</t>
+          <t>2,77; 4,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,72; 10,05</t>
+          <t>6,74; 9,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,4; 6,92</t>
+          <t>5,37; 6,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,07; 4,7</t>
+          <t>4,06; 4,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,51</t>
+          <t>3,39; 5,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,17; 8,57</t>
+          <t>6,13; 8,59</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,97; 6,27</t>
+          <t>5,04; 6,26</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,55; 4,08</t>
+          <t>3,55; 4,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,56</t>
+          <t>3,2; 4,56</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,5; 2,18</t>
+          <t>1,5; 2,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,0; 2,77</t>
+          <t>1,96; 2,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,19; 7,28</t>
+          <t>5,2; 7,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,21; 14,91</t>
+          <t>10,04; 14,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,11; 6,98</t>
+          <t>4,2; 7,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,9; 5,1</t>
+          <t>3,88; 5,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,3; 10,01</t>
+          <t>7,26; 10,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,37; 14,01</t>
+          <t>10,38; 14,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,99; 4,82</t>
+          <t>2,95; 4,69</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,0</t>
+          <t>3,16; 3,96</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,51; 8,31</t>
+          <t>6,49; 8,3</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,69; 13,49</t>
+          <t>10,73; 13,65</t>
         </is>
       </c>
     </row>
@@ -1556,17 +1556,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,46; 3,98</t>
+          <t>2,45; 4,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,62; 3,28</t>
+          <t>2,64; 3,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,61; 10,34</t>
+          <t>7,7; 10,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1576,42 +1576,42 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,94; 5,3</t>
+          <t>3,98; 5,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,39; 5,13</t>
+          <t>4,37; 5,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,22; 12,38</t>
+          <t>10,17; 12,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,37; 23,92</t>
+          <t>14,78; 24,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,58; 4,63</t>
+          <t>3,57; 4,6</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,72; 4,26</t>
+          <t>3,71; 4,24</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,46; 11,16</t>
+          <t>9,54; 11,17</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,99; 23,0</t>
+          <t>10,58; 22,71</t>
         </is>
       </c>
     </row>
@@ -1696,22 +1696,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,13; 6,98</t>
+          <t>5,19; 6,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,16; 6,23</t>
+          <t>5,16; 6,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,64; 4,2</t>
+          <t>3,64; 4,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,33; 4,16</t>
+          <t>3,33; 4,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1721,37 +1721,37 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,76; 7,62</t>
+          <t>6,79; 7,59</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,07; 5,85</t>
+          <t>5,08; 5,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,98; 5,83</t>
+          <t>4,99; 5,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,88; 8,27</t>
+          <t>6,87; 8,25</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,3; 7,01</t>
+          <t>6,3; 6,99</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,56; 5,09</t>
+          <t>4,56; 5,1</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,42; 5,06</t>
+          <t>4,43; 5,06</t>
         </is>
       </c>
     </row>
@@ -1836,27 +1836,27 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,34; 4,03</t>
+          <t>3,32; 4,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,51; 4,97</t>
+          <t>4,49; 4,94</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,88; 6,67</t>
+          <t>5,9; 6,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,07; 6,97</t>
+          <t>5,08; 6,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,5; 6,22</t>
+          <t>5,43; 6,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1866,32 +1866,32 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,09; 8,87</t>
+          <t>8,1; 8,86</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7,06; 8,2</t>
+          <t>7,02; 8,24</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,71; 5,24</t>
+          <t>4,73; 5,25</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5,7; 6,02</t>
+          <t>5,7; 6,01</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7,3; 7,85</t>
+          <t>7,31; 7,89</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,44; 7,52</t>
+          <t>6,45; 7,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q02D_LAB-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q02D_LAB-Provincia-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,64</t>
+          <t>8,41</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,75</t>
+          <t>5,86</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,53</t>
+          <t>6,59</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,63</t>
+          <t>1,8; 3,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,86; 7,58</t>
+          <t>5,86; 7,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,29</t>
+          <t>5,68; 8,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 22,84</t>
+          <t>2,64; 23,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,82; 4,35</t>
+          <t>2,81; 4,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,15; 9,49</t>
+          <t>8,19; 9,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,07; 12,42</t>
+          <t>10,05; 12,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,18; 9,83</t>
+          <t>4,71; 8,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,61; 3,78</t>
+          <t>2,62; 3,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,36; 8,51</t>
+          <t>7,4; 8,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,42; 10,35</t>
+          <t>8,41; 10,41</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,57; 14,03</t>
+          <t>4,61; 11,55</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,03</t>
+          <t>12,43</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,8</t>
+          <t>11,06</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,52</t>
+          <t>11,31</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,07; 7,29</t>
+          <t>5,03; 7,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,22; 7,35</t>
+          <t>6,29; 7,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,4; 12,59</t>
+          <t>9,5; 12,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,21; 23,16</t>
+          <t>6,86; 20,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,67; 9,36</t>
+          <t>7,67; 9,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,43; 8,54</t>
+          <t>7,46; 8,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,87; 13,5</t>
+          <t>10,94; 13,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,62; 13,51</t>
+          <t>8,58; 13,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,92; 8,38</t>
+          <t>6,87; 8,32</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,17; 7,97</t>
+          <t>7,19; 7,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,73; 12,94</t>
+          <t>10,69; 12,84</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,22; 14,48</t>
+          <t>9,24; 13,76</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,68</t>
+          <t>17,16</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,86</t>
+          <t>10,84</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,73</t>
+          <t>13,57</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,87</t>
+          <t>1,45; 3,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,63</t>
+          <t>2,49; 3,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,24; 9,92</t>
+          <t>7,15; 9,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,34; 21,08</t>
+          <t>10,93; 21,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,04; 4,67</t>
+          <t>3,08; 4,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,21; 5,25</t>
+          <t>4,23; 5,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,39; 12,92</t>
+          <t>9,44; 12,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,44; 14,46</t>
+          <t>8,54; 14,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 3,59</t>
+          <t>2,53; 3,56</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,59; 4,41</t>
+          <t>3,62; 4,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,71; 10,95</t>
+          <t>8,79; 10,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,1; 15,95</t>
+          <t>10,59; 17,08</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,49</t>
+          <t>5,47</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,92</t>
+          <t>10,6</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,3</t>
+          <t>8,87</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,2</t>
+          <t>1,5; 2,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,96; 6,46</t>
+          <t>4,98; 6,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,97; 7,98</t>
+          <t>4,99; 7,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,07; 6,9</t>
+          <t>4,24; 6,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,38; 5,1</t>
+          <t>3,32; 5,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,44; 8,83</t>
+          <t>7,49; 8,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,05; 8,99</t>
+          <t>7,18; 9,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,28; 13,37</t>
+          <t>8,97; 12,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,64; 3,71</t>
+          <t>2,64; 3,76</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 7,76</t>
+          <t>6,72; 7,76</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,56; 8,29</t>
+          <t>6,53; 8,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,87; 11,44</t>
+          <t>7,46; 10,83</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,58</t>
+          <t>3,42</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,33</t>
+          <t>4,6</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,17; 7,51</t>
+          <t>4,17; 7,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,05; 5,91</t>
+          <t>4,0; 5,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,8; 3,63</t>
+          <t>2,78; 3,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,77; 4,37</t>
+          <t>2,6; 4,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,74; 9,89</t>
+          <t>6,82; 10,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,37; 6,97</t>
+          <t>5,36; 6,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,06; 4,75</t>
+          <t>4,08; 4,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,39; 5,65</t>
+          <t>3,45; 5,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,13; 8,59</t>
+          <t>6,19; 8,51</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,04; 6,26</t>
+          <t>5,1; 6,25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,55; 4,12</t>
+          <t>3,53; 4,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,2; 4,56</t>
+          <t>3,23; 4,56</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11,96</t>
+          <t>11,8</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11,98</t>
+          <t>12,07</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,97</t>
+          <t>11,95</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,5; 2,19</t>
+          <t>1,5; 2,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,96; 2,79</t>
+          <t>1,97; 2,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,2; 7,19</t>
+          <t>5,21; 7,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,04; 14,72</t>
+          <t>10,22; 14,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,2; 7,29</t>
+          <t>4,26; 7,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,88; 5,05</t>
+          <t>3,86; 5,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,26; 10,21</t>
+          <t>7,27; 9,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,38; 14,1</t>
+          <t>10,58; 14,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,95; 4,69</t>
+          <t>3,04; 4,83</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,16; 3,96</t>
+          <t>3,15; 3,99</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,49; 8,3</t>
+          <t>6,56; 8,37</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,73; 13,65</t>
+          <t>10,76; 13,71</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11,85</t>
+          <t>12,4</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>20,49</t>
+          <t>20,81</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,01</t>
+          <t>18,73</t>
         </is>
       </c>
     </row>
@@ -1556,17 +1556,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,04</t>
+          <t>2,5; 4,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,64; 3,32</t>
+          <t>2,68; 3,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,7; 10,37</t>
+          <t>7,86; 10,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1576,42 +1576,42 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,98; 5,38</t>
+          <t>3,94; 5,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,37; 5,12</t>
+          <t>4,39; 5,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,17; 12,38</t>
+          <t>10,17; 12,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,78; 24,0</t>
+          <t>14,7; 26,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,57; 4,6</t>
+          <t>3,55; 4,66</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,71; 4,24</t>
+          <t>3,69; 4,25</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,54; 11,17</t>
+          <t>9,48; 11,19</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,58; 22,71</t>
+          <t>11,95; 24,81</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,69</t>
+          <t>3,73</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5,37</t>
+          <t>5,54</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,73</t>
+          <t>4,83</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,19; 6,92</t>
+          <t>5,28; 7,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,16; 6,22</t>
+          <t>5,18; 6,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,64; 4,18</t>
+          <t>3,64; 4,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,33; 4,15</t>
+          <t>3,4; 4,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,73; 9,6</t>
+          <t>7,68; 9,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,79; 7,59</t>
+          <t>6,79; 7,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,08; 5,9</t>
+          <t>5,07; 5,82</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,99; 5,83</t>
+          <t>5,12; 5,98</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,87; 8,25</t>
+          <t>6,9; 8,18</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,3; 6,99</t>
+          <t>6,32; 6,97</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,56; 5,1</t>
+          <t>4,55; 5,13</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,43; 5,06</t>
+          <t>4,52; 5,17</t>
         </is>
       </c>
     </row>
@@ -1783,14 +1783,14 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>5,72</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>5,82</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>5,82</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
           <t>6,6</t>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>7,61</t>
+          <t>7,67</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,95</t>
+          <t>6,92</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,32; 4,0</t>
+          <t>3,35; 4,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,49; 4,94</t>
+          <t>4,5; 4,96</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,9; 6,7</t>
+          <t>5,89; 6,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,08; 6,92</t>
+          <t>5,03; 6,64</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,43; 6,19</t>
+          <t>5,51; 6,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,4; 6,82</t>
+          <t>6,41; 6,83</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,1; 8,86</t>
+          <t>8,14; 8,88</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7,02; 8,24</t>
+          <t>7,1; 8,3</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,73; 5,25</t>
+          <t>4,72; 5,26</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5,7; 6,01</t>
+          <t>5,7; 6,03</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7,31; 7,89</t>
+          <t>7,29; 7,88</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,45; 7,49</t>
+          <t>6,47; 7,45</t>
         </is>
       </c>
     </row>
